--- a/Proyecto/data/PowerFlow_Results_Study1/res_line/i_ka.xlsx
+++ b/Proyecto/data/PowerFlow_Results_Study1/res_line/i_ka.xlsx
@@ -394,22 +394,22 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.2132043269903931</v>
+        <v>0.2132043269903937</v>
       </c>
       <c r="C2">
-        <v>0.006422945860354288</v>
+        <v>0.006422945860354242</v>
       </c>
       <c r="D2">
-        <v>0.3295632438689806</v>
+        <v>0.3295632438689813</v>
       </c>
       <c r="E2">
         <v>1.137199872713469</v>
       </c>
       <c r="F2">
-        <v>0.9366469280734794</v>
+        <v>0.9366469280734795</v>
       </c>
       <c r="G2">
-        <v>0.4343468020202013</v>
+        <v>0.434346802020201</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -417,22 +417,22 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.2080955197496194</v>
+        <v>0.2080955197496192</v>
       </c>
       <c r="C3">
-        <v>0.006429880469779391</v>
+        <v>0.006429880469779969</v>
       </c>
       <c r="D3">
-        <v>0.3392391408953851</v>
+        <v>0.3392391408953823</v>
       </c>
       <c r="E3">
-        <v>1.136057303257335</v>
+        <v>1.136057303257334</v>
       </c>
       <c r="F3">
-        <v>0.9401794835277215</v>
+        <v>0.9401794835277197</v>
       </c>
       <c r="G3">
-        <v>0.4475084420161592</v>
+        <v>0.4475084420161575</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -440,22 +440,22 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.2048959179398325</v>
+        <v>0.2048959179398327</v>
       </c>
       <c r="C4">
         <v>0.006434085097676223</v>
       </c>
       <c r="D4">
-        <v>0.3459083203537385</v>
+        <v>0.3459083203537395</v>
       </c>
       <c r="E4">
         <v>1.135486855978517</v>
       </c>
       <c r="F4">
-        <v>0.9425414659629291</v>
+        <v>0.9425414659629298</v>
       </c>
       <c r="G4">
-        <v>0.4560025060209243</v>
+        <v>0.456002506020926</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -463,22 +463,22 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.2025390604130677</v>
+        <v>0.2025390604130673</v>
       </c>
       <c r="C5">
-        <v>0.006436939962453582</v>
+        <v>0.006436939962453581</v>
       </c>
       <c r="D5">
-        <v>0.3514577284764431</v>
+        <v>0.3514577284764419</v>
       </c>
       <c r="E5">
-        <v>1.135551687130771</v>
+        <v>1.135551687130772</v>
       </c>
       <c r="F5">
-        <v>0.9447698102897499</v>
+        <v>0.9447698102897505</v>
       </c>
       <c r="G5">
-        <v>0.4627834910143276</v>
+        <v>0.4627834910143271</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -486,13 +486,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.2064197451804202</v>
+        <v>0.2064197451804204</v>
       </c>
       <c r="C6">
-        <v>0.006431787165541156</v>
+        <v>0.00643178716554053</v>
       </c>
       <c r="D6">
-        <v>0.3432823688476047</v>
+        <v>0.343282368847605</v>
       </c>
       <c r="E6">
         <v>1.136490874232607</v>
@@ -509,22 +509,22 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0.2107519030137681</v>
+        <v>0.2107519030137678</v>
       </c>
       <c r="C7">
-        <v>0.006425886056505271</v>
+        <v>0.006425886056505318</v>
       </c>
       <c r="D7">
-        <v>0.3348695568160469</v>
+        <v>0.3348695568160462</v>
       </c>
       <c r="E7">
-        <v>1.137648243590358</v>
+        <v>1.137648243590359</v>
       </c>
       <c r="F7">
-        <v>0.9393423172394134</v>
+        <v>0.9393423172394162</v>
       </c>
       <c r="G7">
-        <v>0.4416009642079329</v>
+        <v>0.4416009642079339</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -532,22 +532,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.2132991775167422</v>
+        <v>0.2132991775167423</v>
       </c>
       <c r="C8">
-        <v>0.006422114728443833</v>
+        <v>0.006422114728442037</v>
       </c>
       <c r="D8">
-        <v>0.3307228593241629</v>
+        <v>0.3307228593241611</v>
       </c>
       <c r="E8">
-        <v>1.138945646880256</v>
+        <v>1.138945646880257</v>
       </c>
       <c r="F8">
-        <v>0.9383127325788069</v>
+        <v>0.9383127325788085</v>
       </c>
       <c r="G8">
-        <v>0.4357679668318941</v>
+        <v>0.4357679668318946</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -558,19 +558,19 @@
         <v>0.2218563688529495</v>
       </c>
       <c r="C9">
-        <v>0.006409720801018204</v>
+        <v>0.006409720801018234</v>
       </c>
       <c r="D9">
-        <v>0.3175794087992144</v>
+        <v>0.3175794087992154</v>
       </c>
       <c r="E9">
-        <v>1.141989262934149</v>
+        <v>1.14198926293415</v>
       </c>
       <c r="F9">
-        <v>0.9335497850794374</v>
+        <v>0.9335497850794368</v>
       </c>
       <c r="G9">
-        <v>0.4153173478928044</v>
+        <v>0.4153173478928038</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -581,10 +581,10 @@
         <v>0.2299989636572276</v>
       </c>
       <c r="C10">
-        <v>0.006397834851745292</v>
+        <v>0.00639783485174528</v>
       </c>
       <c r="D10">
-        <v>0.3074308638767255</v>
+        <v>0.3074308638767264</v>
       </c>
       <c r="E10">
         <v>1.144165994120576</v>
@@ -593,7 +593,7 @@
         <v>0.9283180381617456</v>
       </c>
       <c r="G10">
-        <v>0.3958262955684246</v>
+        <v>0.395826295568424</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -604,19 +604,19 @@
         <v>0.2332947989522099</v>
       </c>
       <c r="C11">
-        <v>0.00639289780137226</v>
+        <v>0.006392897801372854</v>
       </c>
       <c r="D11">
-        <v>0.3042218993747315</v>
+        <v>0.304221899374726</v>
       </c>
       <c r="E11">
-        <v>1.145099614142326</v>
+        <v>1.145099614142324</v>
       </c>
       <c r="F11">
-        <v>0.9262598637842282</v>
+        <v>0.9262598637842258</v>
       </c>
       <c r="G11">
-        <v>0.3881884644369121</v>
+        <v>0.3881884644369082</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -624,22 +624,22 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.2344045707795424</v>
+        <v>0.2344045707795432</v>
       </c>
       <c r="C12">
-        <v>0.006391364007243092</v>
+        <v>0.006391364007243078</v>
       </c>
       <c r="D12">
-        <v>0.303037678065681</v>
+        <v>0.3030376780656822</v>
       </c>
       <c r="E12">
-        <v>1.145044311258706</v>
+        <v>1.145044311258708</v>
       </c>
       <c r="F12">
-        <v>0.925196145972547</v>
+        <v>0.9251961459725478</v>
       </c>
       <c r="G12">
-        <v>0.3852975550070643</v>
+        <v>0.3852975550070651</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -647,10 +647,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0.2393010346883264</v>
+        <v>0.2393010346883259</v>
       </c>
       <c r="C13">
-        <v>0.006384304172003918</v>
+        <v>0.006384304172003919</v>
       </c>
       <c r="D13">
         <v>0.2989156013152073</v>
@@ -659,10 +659,10 @@
         <v>1.145328943269129</v>
       </c>
       <c r="F13">
-        <v>0.9210414834114925</v>
+        <v>0.9210414834114934</v>
       </c>
       <c r="G13">
-        <v>0.3732260662999746</v>
+        <v>0.373226066299974</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -673,19 +673,19 @@
         <v>0.2374579331270106</v>
       </c>
       <c r="C14">
-        <v>0.006387168704430554</v>
+        <v>0.006387168704431769</v>
       </c>
       <c r="D14">
-        <v>0.3000364268972727</v>
+        <v>0.3000364268972712</v>
       </c>
       <c r="E14">
-        <v>1.144722039210675</v>
+        <v>1.144722039210673</v>
       </c>
       <c r="F14">
-        <v>0.9221005684370522</v>
+        <v>0.9221005684370527</v>
       </c>
       <c r="G14">
-        <v>0.3772673820767403</v>
+        <v>0.3772673820767383</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -693,22 +693,22 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0.226332165733118</v>
+        <v>0.2263321657331178</v>
       </c>
       <c r="C15">
-        <v>0.006403524211464995</v>
+        <v>0.006403524211462562</v>
       </c>
       <c r="D15">
-        <v>0.3111360830494259</v>
+        <v>0.3111360830494266</v>
       </c>
       <c r="E15">
         <v>1.142446372607466</v>
       </c>
       <c r="F15">
-        <v>0.9299283299904926</v>
+        <v>0.9299283299904949</v>
       </c>
       <c r="G15">
-        <v>0.4038160181970541</v>
+        <v>0.4038160181970563</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -716,22 +716,22 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0.2215568806826623</v>
+        <v>0.2215568806826619</v>
       </c>
       <c r="C16">
-        <v>0.006410710231673611</v>
+        <v>0.006410710231674799</v>
       </c>
       <c r="D16">
-        <v>0.3170098708129383</v>
+        <v>0.3170098708129384</v>
       </c>
       <c r="E16">
-        <v>1.1405038047086</v>
+        <v>1.140503804708599</v>
       </c>
       <c r="F16">
-        <v>0.9323310619313949</v>
+        <v>0.9323310619313957</v>
       </c>
       <c r="G16">
-        <v>0.4147034197187782</v>
+        <v>0.4147034197187781</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -739,22 +739,22 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0.2283375780243949</v>
+        <v>0.2283375780243951</v>
       </c>
       <c r="C17">
-        <v>0.006401030961882179</v>
+        <v>0.006401030961880371</v>
       </c>
       <c r="D17">
-        <v>0.3080230522462659</v>
+        <v>0.308023052246267</v>
       </c>
       <c r="E17">
-        <v>1.141825337043156</v>
+        <v>1.141825337043157</v>
       </c>
       <c r="F17">
-        <v>0.9274779818617656</v>
+        <v>0.9274779818617653</v>
       </c>
       <c r="G17">
-        <v>0.3979504101273377</v>
+        <v>0.397950410127338</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -762,13 +762,13 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0.2421314990044132</v>
+        <v>0.2421314990044134</v>
       </c>
       <c r="C18">
-        <v>0.00638020554834533</v>
+        <v>0.006380205548345892</v>
       </c>
       <c r="D18">
-        <v>0.297061842801031</v>
+        <v>0.29706184280103</v>
       </c>
       <c r="E18">
         <v>1.145365523983547</v>
@@ -777,7 +777,7 @@
         <v>0.9185249509052841</v>
       </c>
       <c r="G18">
-        <v>0.3662756676150831</v>
+        <v>0.3662756676150848</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -785,22 +785,22 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0.2583179313965586</v>
+        <v>0.2583179313965574</v>
       </c>
       <c r="C19">
-        <v>0.006354265366928388</v>
+        <v>0.006354265366928984</v>
       </c>
       <c r="D19">
-        <v>0.2965588548864761</v>
+        <v>0.2965588548864713</v>
       </c>
       <c r="E19">
-        <v>1.149985955596259</v>
+        <v>1.149985955596258</v>
       </c>
       <c r="F19">
-        <v>0.9086332589206444</v>
+        <v>0.9086332589206417</v>
       </c>
       <c r="G19">
-        <v>0.3328025118018199</v>
+        <v>0.3328025118018166</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -808,22 +808,22 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0.2764906455302315</v>
+        <v>0.2764906455302311</v>
       </c>
       <c r="C20">
-        <v>0.006323196735385583</v>
+        <v>0.006323196735385575</v>
       </c>
       <c r="D20">
-        <v>0.3111373317578303</v>
+        <v>0.3111373317578313</v>
       </c>
       <c r="E20">
-        <v>1.15602359604749</v>
+        <v>1.156023596047488</v>
       </c>
       <c r="F20">
-        <v>0.8985344193994461</v>
+        <v>0.8985344193994454</v>
       </c>
       <c r="G20">
-        <v>0.3012605858180169</v>
+        <v>0.3012605858180172</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -831,22 +831,22 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0.2919356506585698</v>
+        <v>0.2919356506585694</v>
       </c>
       <c r="C21">
-        <v>0.006295480017200263</v>
+        <v>0.006295480017200265</v>
       </c>
       <c r="D21">
-        <v>0.3340073478296133</v>
+        <v>0.3340073478296101</v>
       </c>
       <c r="E21">
         <v>1.161139631134537</v>
       </c>
       <c r="F21">
-        <v>0.8900819699428045</v>
+        <v>0.8900819699428044</v>
       </c>
       <c r="G21">
-        <v>0.279972264796354</v>
+        <v>0.2799722647963533</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -854,22 +854,22 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0.2760906814649456</v>
+        <v>0.2760906814649461</v>
       </c>
       <c r="C22">
-        <v>0.006323732710207526</v>
+        <v>0.006323732710208117</v>
       </c>
       <c r="D22">
-        <v>0.3107106298412529</v>
+        <v>0.3107106298412514</v>
       </c>
       <c r="E22">
         <v>1.156378873467893</v>
       </c>
       <c r="F22">
-        <v>0.8992462399447289</v>
+        <v>0.899246239944731</v>
       </c>
       <c r="G22">
-        <v>0.3022815520182171</v>
+        <v>0.3022815520182182</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -877,22 +877,22 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>0.2532998032067698</v>
+        <v>0.2532998032067696</v>
       </c>
       <c r="C23">
-        <v>0.00636220592964943</v>
+        <v>0.006362205929648833</v>
       </c>
       <c r="D23">
-        <v>0.2955699902836857</v>
+        <v>0.2955699902836845</v>
       </c>
       <c r="E23">
         <v>1.149246858218863</v>
       </c>
       <c r="F23">
-        <v>0.9123844921420644</v>
+        <v>0.9123844921420654</v>
       </c>
       <c r="G23">
-        <v>0.3433763238784911</v>
+        <v>0.3433763238784914</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -900,22 +900,22 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0.2352644433744861</v>
+        <v>0.2352644433744859</v>
       </c>
       <c r="C24">
-        <v>0.006390391785186935</v>
+        <v>0.006390391785188126</v>
       </c>
       <c r="D24">
-        <v>0.3018295809485428</v>
+        <v>0.3018295809485401</v>
       </c>
       <c r="E24">
         <v>1.144423243297414</v>
       </c>
       <c r="F24">
-        <v>0.923790987358595</v>
+        <v>0.9237909873585939</v>
       </c>
       <c r="G24">
-        <v>0.3825269645021423</v>
+        <v>0.382526964502139</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -923,22 +923,22 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0.2217183939878982</v>
+        <v>0.2217183939878981</v>
       </c>
       <c r="C25">
-        <v>0.00644006893682501</v>
+        <v>0.006440068936825596</v>
       </c>
       <c r="D25">
-        <v>0.2672589833365457</v>
+        <v>0.2672589833365518</v>
       </c>
       <c r="E25">
-        <v>1.061006172619334</v>
+        <v>1.061006172619336</v>
       </c>
       <c r="F25">
-        <v>0.8522958100332538</v>
+        <v>0.8522958100332552</v>
       </c>
       <c r="G25">
-        <v>0.3392208350379744</v>
+        <v>0.3392208350379783</v>
       </c>
     </row>
   </sheetData>
